--- a/cashier_dataset.xlsx
+++ b/cashier_dataset.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8520"/>
+    <workbookView windowWidth="23040" windowHeight="9120"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="167">
   <si>
     <t>S.No</t>
   </si>
@@ -522,6 +522,12 @@
   </si>
   <si>
     <t>Salman</t>
+  </si>
+  <si>
+    <t>Total Withdrawals</t>
+  </si>
+  <si>
+    <t>Total Deposits</t>
   </si>
 </sst>
 </file>
@@ -534,7 +540,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -556,6 +562,13 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -702,7 +715,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -712,6 +725,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -902,7 +921,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1017,6 +1036,32 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -1134,55 +1179,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1197,74 +1239,77 @@
     <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1322,10 +1367,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1853,7 +1901,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B3:Q34"/>
+  <dimension ref="B2:Q39"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="18" customWidth="1"/>
@@ -1871,6 +1919,7 @@
     <col min="16" max="17" width="14.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="2" ht="15.15"/>
     <row r="3" spans="2:17">
       <c r="B3" s="1" t="s">
         <v>0</v>
@@ -3479,7 +3528,7 @@
       <c r="K34" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="L34" s="19" t="str">
+      <c r="L34" s="17" t="str">
         <f>IF(K34="Cheque","CHQ"&amp;TEXT(1000+COUNTIF($K$5:K34,"Cheque"),"0"),"N/A")</f>
         <v>N/A</v>
       </c>
@@ -3495,8 +3544,26 @@
       <c r="P34" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="Q34" s="20" t="s">
+      <c r="Q34" s="19" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="38" ht="15.15" spans="2:17">
+      <c r="G38" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="H38" s="21">
+        <f>SUM(H5:H34)</f>
+        <v>318000</v>
+      </c>
+    </row>
+    <row r="39" ht="15.15" spans="2:17">
+      <c r="G39" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="H39" s="21">
+        <f>SUM(I5:I34)</f>
+        <v>135100</v>
       </c>
     </row>
   </sheetData>
